--- a/data/describe/few_shot/few_shot_FA_label.xlsx
+++ b/data/describe/few_shot/few_shot_FA_label.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
   <si>
     <t>User</t>
   </si>
@@ -19,23 +19,31 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>Here is the factor description in terms of the features of a person: ```The factor is very strongly positively associated with the feature that they feel comfortable around people, strongly positively associated with the feature that they talk to a lot of different people at parties, strongly positively associated with the feature that they start conversations, strongly positively associated with the feature that they are the life of the party, moderately positively associated with the feature that they interested in people. The factor is strongly negatively associated with the feature that they are quiet around strangers, strongly negatively associated with the feature that they keep in the background, strongly negatively associated with the feature that they not really interested in others, strongly negatively associated with the feature that they have little to say, moderately negatively associated with the feature that they dont talk a lot. ```</t>
+    <t>The existing names are: reserved vs outgoing, anxious vs imaginative. In this case, it is important that the name you now make is different from these names.
+Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they dont like to draw attention to themself ismoderately associated with the x pole , the feature that they get chores done right away ismoderately associated with the x pole , the feature that they take time out for others isweakly associated with the x pole , the feature that they are quiet around strangers isweakly associated with the x pole , the feature that they are always prepared isweakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that they insult people is moderately associated with the y pole , the feature that they often forget to put things back in their proper place is weakly associated with the y pole , the feature that they are the life of the party is weakly associated with the y pole , the feature that they shirk their duties is weakly associated with the y pole , the feature that they leave their belongings around is weakly associated with the y pole.```</t>
   </si>
   <si>
-    <t>introverted vs extraverted</t>
+    <t>shy but responsible vs party animal</t>
   </si>
   <si>
-    <t>Here is the factor description in terms of the features of a football player: ```The factor is very strongly positively associated with the feature that final third passes, very strongly positively associated with the feature that final third receptions, very strongly positively associated with the feature that smart passes, very strongly positively associated with the feature that adjusted, strongly positively associated with the feature that ground duels. The factor is weakly negatively associated with the feature that air duels, very weakly negatively associated with the feature that non-penalty expected goals. ```</t>
+    <t>An existing name is: detached vs engaged. In this case, it is important that the name you now make is different from this name.
+Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they worry about things is strongly associated with the x pole , the feature that they have a vivid imagination is moderately associated with the x pole , the feature that they get upset easily is moderately associated with the x pole , the feature that they change their mood a lot is moderately associated with the x pole , the feature that they have excellent ideas is moderately associated with the x pole . There are no features used to name the y pole. You should describe it simply as the opposite of the x pole, which you already got information about. If possible use a negation such as 'not x' to name the y pole. ```"</t>
   </si>
   <si>
-    <t>creative passer vs aerial dueler</t>
+    <t>worrier vs no worries</t>
   </si>
   <si>
-    <t>The existing names are: religious vs secular, confident vs doubtful. In this case, it is important that the name you now make is different from these names.
-Here is the factor description in terms of the features of a country: ```The factor is very strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a sport or recreational organization?, very strongly positively associated with the feature that Are you an active member, inactive member, or not a member of another type of organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of an art, music, or educational organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a consumer organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a labor union?. The factor is very strongly negatively associated with the feature that How frequently does alcohol consumption in the streets occur in your neighborhood?, very strongly negatively associated with the feature that Please tell me for the following statement how essential you think it is as a characteristic of democracy: Governments tax the rich and subsidize the poor., very strongly negatively associated with the feature that Have you been the victim of a crime during the past year?, strongly negatively associated with the feature that Has someone in your immediate family been the victim of a crime during the past year?, strongly negatively associated with the feature that Do you agree that science and technology will provide more opportunities for the next generation?. ```</t>
+    <t>Output the name in x vs y format only. We refer to x in this format as the x pole and y as the y pole.
+Here is the factor description in terms of the features of a country: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that How much confidence do you have in political parties? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole , the feature that In the future, would it be a good thing if less importance is placed on work?  (on a scale of 'good' to 'bad') is weakly associated with the x pole , the feature that How much confidence do you have in the parliament? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that Is 'stealing property' can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'someone accepting a bribe in the course of their duties' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'violence against other people' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is ' for a man to beat his wife ' can always be justified, never be justified, or something in between:(on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole .```"</t>
   </si>
   <si>
-    <t>community membership vs insecurity and crime</t>
+    <t>belief in society vs justifying crime</t>
+  </si>
+  <si>
+    <t>Here is the factor description in terms of the features of a football player: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that air duels won adjusted per 90 minutes is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that final third passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that final third receptions adjusted per 90 minutes is very strongly associated with the y pole , the feature that smart passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that key passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that ground duels won adjusted per 90 minutes is strongly associated with the y pole .```"</t>
+  </si>
+  <si>
+    <t>good in air vs creative maestro</t>
   </si>
 </sst>
 </file>
@@ -76,7 +84,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -91,16 +99,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -117,16 +125,16 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -149,8 +157,8 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -349,17 +357,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -386,10 +394,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -628,12 +636,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -910,7 +918,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -937,10 +945,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1202,7 +1210,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" ht="176" customHeight="1">
+    <row r="2" ht="313.15" customHeight="1">
       <c r="A2" t="s" s="4">
         <v>2</v>
       </c>
@@ -1213,7 +1221,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" ht="143.8" customHeight="1">
+    <row r="3" ht="233.45" customHeight="1">
       <c r="A3" t="s" s="4">
         <v>4</v>
       </c>
@@ -1235,9 +1243,13 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
+    <row r="5" ht="359.65" customHeight="1">
+      <c r="A5" t="s" s="5">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>9</v>
+      </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>

--- a/data/describe/few_shot/few_shot_FA_label.xlsx
+++ b/data/describe/few_shot/few_shot_FA_label.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6677123-729A-481A-8A45-4F3852BCD27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>User</t>
   </si>
@@ -19,53 +33,40 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>The existing names are: reserved vs outgoing, anxious vs imaginative. In this case, it is important that the name you now make is different from these names.
-Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they dont like to draw attention to themself ismoderately associated with the x pole , the feature that they get chores done right away ismoderately associated with the x pole , the feature that they take time out for others isweakly associated with the x pole , the feature that they are quiet around strangers isweakly associated with the x pole , the feature that they are always prepared isweakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that they insult people is moderately associated with the y pole , the feature that they often forget to put things back in their proper place is weakly associated with the y pole , the feature that they are the life of the party is weakly associated with the y pole , the feature that they shirk their duties is weakly associated with the y pole , the feature that they leave their belongings around is weakly associated with the y pole.```</t>
-  </si>
-  <si>
     <t>shy but responsible vs party animal</t>
-  </si>
-  <si>
-    <t>An existing name is: detached vs engaged. In this case, it is important that the name you now make is different from this name.
-Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they worry about things is strongly associated with the x pole , the feature that they have a vivid imagination is moderately associated with the x pole , the feature that they get upset easily is moderately associated with the x pole , the feature that they change their mood a lot is moderately associated with the x pole , the feature that they have excellent ideas is moderately associated with the x pole . There are no features used to name the y pole. You should describe it simply as the opposite of the x pole, which you already got information about. If possible use a negation such as 'not x' to name the y pole. ```"</t>
   </si>
   <si>
     <t>worrier vs no worries</t>
   </si>
   <si>
-    <t>Output the name in x vs y format only. We refer to x in this format as the x pole and y as the y pole.
-Here is the factor description in terms of the features of a country: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that How much confidence do you have in political parties? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole , the feature that In the future, would it be a good thing if less importance is placed on work?  (on a scale of 'good' to 'bad') is weakly associated with the x pole , the feature that How much confidence do you have in the parliament? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that Is 'stealing property' can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'someone accepting a bribe in the course of their duties' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'violence against other people' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is ' for a man to beat his wife ' can always be justified, never be justified, or something in between:(on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole .```"</t>
-  </si>
-  <si>
     <t>belief in society vs justifying crime</t>
   </si>
   <si>
-    <t>Here is the factor description in terms of the features of a football player: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that air duels won adjusted per 90 minutes is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that final third passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that final third receptions adjusted per 90 minutes is very strongly associated with the y pole , the feature that smart passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that key passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that ground duels won adjusted per 90 minutes is strongly associated with the y pole .```"</t>
+    <t>good in air vs creative maestro</t>
   </si>
   <si>
-    <t>good in air vs creative maestro</t>
+    <t>The existing names are: reserved vs outgoing, anxious vs imaginative. In this case, it is important that the name you now make is different from these names.
+Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they dont like to draw attention to themself ismoderately associated with the x pole , the feature that they get chores done right away ismoderately associated with the x pole , the feature that they take time out for others isweakly associated with the x pole , the feature that they are quiet around strangers isweakly associated with the x pole , the feature that they are always prepared isweakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that they insult people is moderately associated with the y pole , the feature that they often forget to put things back in their proper place is weakly associated with the y pole , the feature that they are the life of the party is weakly associated with the y pole , the feature that they shirk their duties is weakly associated with the y pole , the feature that they leave their belongings around is weakly associated with the y pole.´´´</t>
+  </si>
+  <si>
+    <t>An existing name is: detached vs engaged. In this case, it is important that the name you now make is different from this name.
+Here is the factor description in terms of the features of a person: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that they worry about things is strongly associated with the x pole , the feature that they have a vivid imagination is moderately associated with the x pole , the feature that they get upset easily is moderately associated with the x pole , the feature that they change their mood a lot is moderately associated with the x pole , the feature that they have excellent ideas is moderately associated with the x pole . There are no features used to name the y pole. You should describe it simply as the opposite of the x pole, which you already got information about. If possible use a negation such as 'not x' to name the y pole. ´´´</t>
+  </si>
+  <si>
+    <t>Output the name in x vs y format only. We refer to x in this format as the x pole and y as the y pole.
+Here is the factor description in terms of the features of a country: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that How much confidence do you have in political parties? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole , the feature that In the future, would it be a good thing if less importance is placed on work?  (on a scale of 'good' to 'bad') is weakly associated with the x pole , the feature that How much confidence do you have in the parliament? (on a scale of ' a great deal' to 'none at all') is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that Is 'stealing property' can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'someone accepting a bribe in the course of their duties' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'violence against other people' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is ' for a man to beat his wife ' can always be justified, never be justified, or something in between:(on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole , the feature that Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between:  (on a scale of 'never justifiable' to 'always justifiable') is very strongly associated with the y pole .´´´</t>
+  </si>
+  <si>
+    <t>Here is the factor description in terms of the features of a football player: ```The first features we look at should primarily be used to name the x pole. The higher the value of the association, the more important the feature is for naming the x pole. Here is a list of the features and how important they are for naming the x pole: the feature that air duels won adjusted per 90 minutes is weakly associated with the x pole . The next features we look at should primarily be used to name the y pole. The higher the value of the association, the more important the feature is for naming the y pole. Here is a list of the features and how important they are for naming the y pole: the feature that final third passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that final third receptions adjusted per 90 minutes is very strongly associated with the y pole , the feature that smart passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that key passes adjusted per 90 minutes is very strongly associated with the y pole , the feature that ground duels won adjusted per 90 minutes is strongly associated with the y pole .´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
@@ -114,30 +115,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -148,24 +139,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -367,7 +419,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -385,7 +437,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -414,7 +466,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -439,7 +491,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -464,7 +516,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -489,7 +541,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -514,7 +566,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -539,7 +591,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -564,7 +616,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -589,7 +641,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -614,7 +666,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -627,9 +679,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -646,7 +704,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -664,7 +722,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -689,7 +747,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -714,7 +772,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -739,7 +797,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -764,7 +822,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -789,7 +847,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -814,7 +872,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -839,7 +897,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -864,7 +922,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -889,7 +947,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -902,9 +960,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -918,7 +982,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -936,7 +1000,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -965,7 +1029,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -990,7 +1054,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1015,7 +1079,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1040,7 +1104,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1065,7 +1129,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1090,7 +1154,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1115,7 +1179,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1140,7 +1204,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1165,7 +1229,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1178,111 +1242,118 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.5" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="99.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="43" style="1" customWidth="1"/>
-    <col min="3" max="5" width="8.85156" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="3" max="6" width="8.81640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" ht="313.15" customHeight="1">
-      <c r="A2" t="s" s="4">
+    <row r="2" spans="1:5" ht="313.14999999999998" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>3</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" ht="233.45" customHeight="1">
-      <c r="A3" t="s" s="4">
-        <v>4</v>
+    <row r="3" spans="1:5" ht="233.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
       </c>
-      <c r="B3" t="s" s="4">
-        <v>5</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" ht="352.7" customHeight="1">
-      <c r="A4" t="s" s="4">
-        <v>6</v>
+    <row r="4" spans="1:5" ht="352.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
       </c>
-      <c r="B4" t="s" s="4">
-        <v>7</v>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" ht="359.65" customHeight="1">
-      <c r="A5" t="s" s="5">
-        <v>8</v>
+    <row r="5" spans="1:5" ht="359.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
       </c>
-      <c r="B5" t="s" s="4">
-        <v>9</v>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" ht="13.55" customHeight="1">
+    <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" ht="13.55" customHeight="1">
+    <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" ht="13.55" customHeight="1">
+    <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" ht="13.55" customHeight="1">
+    <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1291,7 +1362,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
